--- a/kawasaki_project/05_試算・管理シート/川崎町_計画書_別添整理表_R8.9.29.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_計画書_別添整理表_R8.9.29.xlsx
@@ -1861,58 +1861,58 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Ｆ 進行管理</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>計画の公表・実施状況の評価・意見聴取の手続</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>認知症基本法第13条第3項が準用する第12条第4項〜第7項</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>なし（第9期は計画の策定以外を行っていない）</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>素案 第6章6-1の表に7つの手続を整理済み。6-4 第1節に5事業として掲げている</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>手続の様式（意見聴取の記録・評価結果の公表の様式）を作成する</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>令和8年9月29日に様式一式（様式1〜5・7シート）を作成した。`05_試算・管理シート/川崎町_認知症_意見聴取記録様式_R8.9.29.xlsx`。厚生労働省「都道府県・市町村向け認知症施策推進計画策定の手引き」3.1（2）及び「認知症の本人の声を施策・事業運営に活かしていくためのヒント」（令和7年度老健事業）の考え方に沿って設計している</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>運用（記録者・保管・個人情報の取扱い・計画書への掲げ方）を町と確定する（確認事項No.146）。聴取の実施（令和8年10〜11月）後に、結果の要約（誰から何件・主な意見）を別添に加える</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>別冊（様式集）</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="I23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>第6章6-1・6-4第1節・第10章10-2</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
@@ -2309,22 +2309,22 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>素案Ver.2.1（第1章〜第10章。目次4頁を含む）</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>継続101事業の本文をどこまで書き下ろすかにより増減する。打合せによる</t>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>素案Ver.2.2（第1章〜第10章。目次4頁を含む）</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Ver.2.1の88頁から5頁増えた（第6章に「新しい認知症観」と本町が目指す姿・本人参画の進め方・部署横断的な検討の場・他の計画との連動・事業の追加候補の表を加えたことによる）。継続101事業の本文をどこまで書き下ろすかにより更に増減する。打合せによる</t>
         </is>
       </c>
     </row>
@@ -2360,11 +2360,11 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>仕様書8の「100頁程度」に収まる</t>
+          <t>仕様書8は「100頁程度」。Ver.2.1の時点では101頁であったが、本文が93頁になったことにより106頁となる。100頁程度の範囲と考えるが、継続101事業を本文に書き下ろす場合は資料編を絞り込む必要がある（別添の置き場所の振り分けを見直す）</t>
         </is>
       </c>
     </row>
@@ -2645,29 +2645,29 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>認知症の人及び家族等からの意見聴取の記録様式</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>認知症基本法第13条第3項が準用する第12条第3項・第7項</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>聴取の日／場所／方法（本人ミーティング・訪問・アンケート）／参加者数／いただいた意見／計画への反映</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>R8.10（聴取の実施前）</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>様式1 実施計画（場・機会／実施予定／対象／聴き方／町の出席者／記録者）／様式2 意見聴取記録票（聴いた場／その日共に何をしたか／参加者／場の設え／本人の声（言葉のまま）／家族等の声／表情・振る舞い・場の雰囲気／写真・イラスト／記録者が気づいたこと／今すぐできること／地域課題への翻訳／関わる施策・事業／フィードバックの予定／庁内・庁外への共有の予定）／様式3 反映台帳（15項目）／様式4 フィードバック記録／様式5 評価時の意見聴取</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>R8.9.29 作成済み（運用は確認事項No.146）</t>
         </is>
       </c>
     </row>

--- a/kawasaki_project/05_試算・管理シート/川崎町_計画書_別添整理表_R8.9.29.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_計画書_別添整理表_R8.9.29.xlsx
@@ -1888,7 +1888,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>令和8年9月29日に様式一式（様式1〜5・7シート）を作成した。`05_試算・管理シート/川崎町_認知症_意見聴取記録様式_R8.9.29.xlsx`。厚生労働省「都道府県・市町村向け認知症施策推進計画策定の手引き」3.1（2）及び「認知症の本人の声を施策・事業運営に活かしていくためのヒント」（令和7年度老健事業）の考え方に沿って設計している</t>
+          <t>令和8年9月29日に様式一式（様式1〜5・7シート）を作成した。`05_試算・管理シート/川崎町_認知症_意見聴取記録様式_R8.9.30.xlsx`。厚生労働省「都道府県・市町村向け認知症施策推進計画策定の手引き」3.1（2）及び「認知症の本人の声を施策・事業運営に活かしていくためのヒント」（令和7年度老健事業）の考え方に沿って設計している</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -2316,15 +2316,15 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>素案Ver.2.2（第1章〜第10章。目次4頁を含む）</t>
+          <t>素案Ver.2.3（第1章〜第10章。目次4頁を含む）</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Ver.2.1の88頁から5頁増えた（第6章に「新しい認知症観」と本町が目指す姿・本人参画の進め方・部署横断的な検討の場・他の計画との連動・事業の追加候補の表を加えたことによる）。継続101事業の本文をどこまで書き下ろすかにより更に増減する。打合せによる</t>
+          <t>Ver.2.1の88頁から9頁増えた。Ver.2.2で第6章に「新しい認知症観」と本町が目指す姿・本人参画の進め方・部署横断的な検討の場・他の計画との連動・事業の追加候補の表を加えて93頁となり、Ver.2.3でレビュー指摘の反映（追加候補の見込量・費用・財源の枠組み、第9章の見込量0のサービスの掲載と0の区分、認知症施策の保険料への影響の財源別の換算表）を加えて97頁となった。継続101事業の本文をどこまで書き下ろすかにより更に増減する。打合せによる</t>
         </is>
       </c>
     </row>
@@ -2360,11 +2360,11 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>仕様書8は「100頁程度」。Ver.2.1の時点では101頁であったが、本文が93頁になったことにより106頁となる。100頁程度の範囲と考えるが、継続101事業を本文に書き下ろす場合は資料編を絞り込む必要がある（別添の置き場所の振り分けを見直す）</t>
+          <t>⚠ 仕様書8は「100頁程度」。Ver.2.1の時点では101頁であったが、本文が97頁になったことにより110頁となり、100頁を10％上回る。打合せで次のいずれかをご判断いただきたい。①資料編を絞り込む（用語解説2頁・パブリックコメント2頁・第9期との読み替え表2頁を別冊に移すと資料編7頁・計104頁）。②本文を圧縮する（第9章の感度分析・第3章の交付金の分析は資料編又は別冊に移せる）。③110頁を「100頁程度」の範囲として許容する。継続101事業を本文に書き下ろす場合（約10頁増）は①②が必要になる</t>
         </is>
       </c>
     </row>
@@ -2469,22 +2469,22 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>（参考）すべて資料編に載せた場合</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>100頁程度を大きく超えるため、上記の振り分けを提案する</t>
+      <c r="C10" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>100頁程度を大きく超えるため、上記の振り分けを提案する（本文97頁のため、すべて資料編に載せると140頁となる）</t>
         </is>
       </c>
     </row>

--- a/kawasaki_project/05_試算・管理シート/川崎町_計画書_別添整理表_R8.9.29.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_計画書_別添整理表_R8.9.29.xlsx
@@ -2316,15 +2316,15 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>素案Ver.2.3（第1章〜第10章。目次4頁を含む）</t>
+          <t>素案Ver.2.4（第1章〜第10章。目次3頁を含む）</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Ver.2.1の88頁から9頁増えた。Ver.2.2で第6章に「新しい認知症観」と本町が目指す姿・本人参画の進め方・部署横断的な検討の場・他の計画との連動・事業の追加候補の表を加えて93頁となり、Ver.2.3でレビュー指摘の反映（追加候補の見込量・費用・財源の枠組み、第9章の見込量0のサービスの掲載と0の区分、認知症施策の保険料への影響の財源別の換算表）を加えて97頁となった。継続101事業の本文をどこまで書き下ろすかにより更に増減する。打合せによる</t>
+          <t>Ver.2.1の88頁から16頁増えた。Ver.2.2で第6章に「新しい認知症観」と本町が目指す姿・本人参画の進め方・部署横断的な検討の場・他の計画との連動・事業の追加候補の表を加えて93頁となり、Ver.2.3でレビュー指摘の反映（追加候補の見込量・費用・財源の枠組み、第9章の見込量0のサービスの掲載と0の区分、認知症施策の保険料への影響の財源別の換算表）を加えて97頁となり、Ver.2.4で大雪地区広域連合の協議用素案との対比による補充（1-5 介護保険制度改正の主な内容、1-6 日常生活圏域の設定、9-1 24時間対応サービスの確保方策・介護施設整備に係る基本方針、9-3 低所得者支援、巻末の図表番号一覧）を加えて104頁となった。継続101事業の本文をどこまで書き下ろすかにより更に増減する。打合せによる</t>
         </is>
       </c>
     </row>
@@ -2360,11 +2360,11 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>⚠ 仕様書8は「100頁程度」。Ver.2.1の時点では101頁であったが、本文が97頁になったことにより110頁となり、100頁を10％上回る。打合せで次のいずれかをご判断いただきたい。①資料編を絞り込む（用語解説2頁・パブリックコメント2頁・第9期との読み替え表2頁を別冊に移すと資料編7頁・計104頁）。②本文を圧縮する（第9章の感度分析・第3章の交付金の分析は資料編又は別冊に移せる）。③110頁を「100頁程度」の範囲として許容する。継続101事業を本文に書き下ろす場合（約10頁増）は①②が必要になる</t>
+          <t>⚠ 仕様書8は「100頁程度」。Ver.2.1の時点では101頁であったが、本文が104頁になったことにより117頁となり、100頁を17％上回る。Ver.2.4で加えた7頁は、国の基本指針・法改正が求める記載事項であり削ることができない。打合せで次のいずれかをご判断いただきたい。①資料編を絞り込む（用語解説2頁・パブリックコメント2頁・第9期との読み替え表2頁を別冊に移すと資料編7頁・計111頁）。②本文を圧縮する（第3章3-3の交付金の枝番レベルの分析 約4頁、第9章9-3の感度分析 約2頁、第6章6-4の143事業の書き下ろし 約6頁を資料編又は別冊に移すと本文92頁・計99頁）。③117頁を「100頁程度」の範囲として許容する。当社は②を提案する。継続101事業を本文に書き下ろす場合（約10頁増）は②が必須となる</t>
         </is>
       </c>
     </row>
@@ -2480,11 +2480,11 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>100頁程度を大きく超えるため、上記の振り分けを提案する（本文97頁のため、すべて資料編に載せると140頁となる）</t>
+          <t>100頁程度を大きく超えるため、上記の振り分けを提案する（本文104頁のため、すべて資料編に載せると147頁となる）</t>
         </is>
       </c>
     </row>

--- a/kawasaki_project/05_試算・管理シート/川崎町_計画書_別添整理表_R8.9.29.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_計画書_別添整理表_R8.9.29.xlsx
@@ -2316,15 +2316,15 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>素案Ver.2.4（第1章〜第10章。目次3頁を含む）</t>
+          <t>素案Ver.2.5（第1章〜第10章。目次3頁を含む）</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Ver.2.1の88頁から16頁増えた。Ver.2.2で第6章に「新しい認知症観」と本町が目指す姿・本人参画の進め方・部署横断的な検討の場・他の計画との連動・事業の追加候補の表を加えて93頁となり、Ver.2.3でレビュー指摘の反映（追加候補の見込量・費用・財源の枠組み、第9章の見込量0のサービスの掲載と0の区分、認知症施策の保険料への影響の財源別の換算表）を加えて97頁となり、Ver.2.4で大雪地区広域連合の協議用素案との対比による補充（1-5 介護保険制度改正の主な内容、1-6 日常生活圏域の設定、9-1 24時間対応サービスの確保方策・介護施設整備に係る基本方針、9-3 低所得者支援、巻末の図表番号一覧）を加えて104頁となった。継続101事業の本文をどこまで書き下ろすかにより更に増減する。打合せによる</t>
+          <t>Ver.2.1の88頁から13頁増えた。Ver.2.2で第6章に「新しい認知症観」と本町が目指す姿・本人参画の進め方・部署横断的な検討の場・他の計画との連動・事業の追加候補の表を加えて93頁となり、Ver.2.3でレビュー指摘の反映（追加候補の見込量・費用・財源の枠組み、第9章の見込量0のサービスの掲載と0の区分、認知症施策の保険料への影響の財源別の換算表）を加えて97頁となり、Ver.2.4で大雪地区広域連合の協議用素案との対比による補充（1-5 介護保険制度改正の主な内容、1-6 日常生活圏域の設定、9-1 24時間対応サービスの確保方策・介護施設整備に係る基本方針、9-3 低所得者支援、巻末の図表番号一覧）を加えて104頁となり、Ver.2.5で書体と文字の大きさを大雪地区広域連合の協議用素案に合わせた（本文10.5→10.0pt・表9.0→8.5pt）ことにより101頁となった。継続101事業の本文をどこまで書き下ろすかにより更に増減する。打合せによる</t>
         </is>
       </c>
     </row>
@@ -2360,11 +2360,11 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>⚠ 仕様書8は「100頁程度」。Ver.2.1の時点では101頁であったが、本文が104頁になったことにより117頁となり、100頁を17％上回る。Ver.2.4で加えた7頁は、国の基本指針・法改正が求める記載事項であり削ることができない。打合せで次のいずれかをご判断いただきたい。①資料編を絞り込む（用語解説2頁・パブリックコメント2頁・第9期との読み替え表2頁を別冊に移すと資料編7頁・計111頁）。②本文を圧縮する（第3章3-3の交付金の枝番レベルの分析 約4頁、第9章9-3の感度分析 約2頁、第6章6-4の143事業の書き下ろし 約6頁を資料編又は別冊に移すと本文92頁・計99頁）。③117頁を「100頁程度」の範囲として許容する。当社は②を提案する。継続101事業を本文に書き下ろす場合（約10頁増）は②が必須となる</t>
+          <t>⚠ 仕様書8は「100頁程度」。Ver.2.1の時点では101頁であったが、本文が101頁になったことにより114頁となり、100頁を14％上回る。Ver.2.5の書体の統一により本文が3頁縮んだ。Ver.2.4で加えた7頁は、国の基本指針・法改正が求める記載事項であり削ることができない。打合せで次のいずれかをご判断いただきたい。①資料編を絞り込む（用語解説2頁・パブリックコメント2頁・第9期との読み替え表2頁を別冊に移すと資料編7頁・計108頁）。②本文を圧縮する（第3章3-3の交付金の枝番レベルの分析 約4頁、第9章9-3の感度分析 約2頁、第6章6-4の143事業の書き下ろし 約6頁を資料編又は別冊に移すと本文89頁・計96頁）。③114頁を「100頁程度」の範囲として許容する。当社は②を提案する。継続101事業を本文に書き下ろす場合（約10頁増）は②が必須となる</t>
         </is>
       </c>
     </row>
@@ -2480,11 +2480,11 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>100頁程度を大きく超えるため、上記の振り分けを提案する（本文104頁のため、すべて資料編に載せると147頁となる）</t>
+          <t>100頁程度を大きく超えるため、上記の振り分けを提案する（本文101頁のため、すべて資料編に載せると144頁となる）</t>
         </is>
       </c>
     </row>
